--- a/data/trans_orig/Predimed_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según adherencia a la dieta mediterránea en 2023</t>
+          <t>Población según adherencia a la dieta mediterránea en 2023 (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80567</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114928</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79565</t>
+          <t>79008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>108654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166314</t>
+          <t>168006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213611</t>
+          <t>213161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368726</t>
+          <t>369494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403087</t>
+          <t>404759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325655</t>
+          <t>324474</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353563</t>
+          <t>354120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703171</t>
+          <t>703621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750468</t>
+          <t>748776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>90668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73497</t>
+          <t>72899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101075</t>
+          <t>99523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138882</t>
+          <t>140603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>183210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336283</t>
+          <t>337478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368646</t>
+          <t>368681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>269969</t>
+          <t>271521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297547</t>
+          <t>298145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619020</t>
+          <t>615980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>660308</t>
+          <t>658587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143645</t>
+          <t>142994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49555</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56581</t>
+          <t>51185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185440</t>
+          <t>186235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499582</t>
+          <t>500233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613461</t>
+          <t>613277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108109</t>
+          <t>106300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125535</t>
+          <t>125451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615452</t>
+          <t>614657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744311</t>
+          <t>749707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162997</t>
+          <t>157848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210681</t>
+          <t>213333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73187</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213341</t>
+          <t>229161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388655</t>
+          <t>388400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744614</t>
+          <t>741962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792298</t>
+          <t>797447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>736115</t>
+          <t>736236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>865435</t>
+          <t>861801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1505262</t>
+          <t>1505517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1680576</t>
+          <t>1664756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>36661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65488</t>
+          <t>64816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116330</t>
+          <t>117826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>250205</t>
+          <t>250951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166408</t>
+          <t>164042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>298051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372934</t>
+          <t>373606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401522</t>
+          <t>401761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>544650</t>
+          <t>543904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>678525</t>
+          <t>677029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>932938</t>
+          <t>935226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1066869</t>
+          <t>1069235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>31425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>68945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100642</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81674</t>
+          <t>81956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120541</t>
+          <t>119289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165699</t>
+          <t>167432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192243</t>
+          <t>192198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>593164</t>
+          <t>594084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>623869</t>
+          <t>624861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>772122</t>
+          <t>773374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>810989</t>
+          <t>810707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>377104</t>
+          <t>383536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>562703</t>
+          <t>567668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>512276</t>
+          <t>495061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>707069</t>
+          <t>697540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>963523</t>
+          <t>957674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1231534</t>
+          <t>1226099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2584898</t>
+          <t>2579933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2770497</t>
+          <t>2764065</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2682050</t>
+          <t>2691579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2876843</t>
+          <t>2894058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5305186</t>
+          <t>5310621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5573197</t>
+          <t>5579046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96673</t>
+          <t>108420</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78895</t>
+          <t>88015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114160</t>
+          <t>129364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92657</t>
+          <t>100494</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79008</t>
+          <t>86387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108654</t>
+          <t>117579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>189330</t>
+          <t>208914</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168006</t>
+          <t>183169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213161</t>
+          <t>234807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>386981</t>
+          <t>417705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>369494</t>
+          <t>396761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404759</t>
+          <t>438110</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>340471</t>
+          <t>372700</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324474</t>
+          <t>355615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>354120</t>
+          <t>386807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>727452</t>
+          <t>790405</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703621</t>
+          <t>764512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748776</t>
+          <t>816150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>483654</t>
+          <t>526125</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>483654</t>
+          <t>526125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>483654</t>
+          <t>526125</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>433128</t>
+          <t>473194</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>433128</t>
+          <t>473194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>433128</t>
+          <t>473194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>916782</t>
+          <t>999319</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>916782</t>
+          <t>999319</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>916782</t>
+          <t>999319</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73498</t>
+          <t>81418</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59465</t>
+          <t>65905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90668</t>
+          <t>100850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86318</t>
+          <t>96806</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72899</t>
+          <t>83237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99523</t>
+          <t>112091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>159817</t>
+          <t>178223</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>140603</t>
+          <t>156660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183210</t>
+          <t>201981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>354648</t>
+          <t>376024</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337478</t>
+          <t>356592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368681</t>
+          <t>391537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>284726</t>
+          <t>312966</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271521</t>
+          <t>297681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>298145</t>
+          <t>326535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>639373</t>
+          <t>688991</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>615980</t>
+          <t>665233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>658587</t>
+          <t>710554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>428146</t>
+          <t>457442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>428146</t>
+          <t>457442</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>428146</t>
+          <t>457442</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>371044</t>
+          <t>409772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>371044</t>
+          <t>409772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>371044</t>
+          <t>409772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>799190</t>
+          <t>867214</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>799190</t>
+          <t>867214</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>799190</t>
+          <t>867214</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83131</t>
+          <t>96766</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142994</t>
+          <t>115624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123245</t>
+          <t>139881</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>120489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186235</t>
+          <t>160945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>560096</t>
+          <t>348077</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500233</t>
+          <t>329219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613277</t>
+          <t>363804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>133311</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106300</t>
+          <t>123011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125451</t>
+          <t>142466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>677647</t>
+          <t>481389</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614657</t>
+          <t>460325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749707</t>
+          <t>500781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>643227</t>
+          <t>444843</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>643227</t>
+          <t>444843</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643227</t>
+          <t>444843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>157664</t>
+          <t>176427</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157664</t>
+          <t>176427</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157664</t>
+          <t>176427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>800892</t>
+          <t>621270</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>800892</t>
+          <t>621270</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>800892</t>
+          <t>621270</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>183584</t>
+          <t>205991</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157848</t>
+          <t>178893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213333</t>
+          <t>235702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76821</t>
+          <t>149609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202386</t>
+          <t>188138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>334842</t>
+          <t>374363</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229161</t>
+          <t>339048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388400</t>
+          <t>411669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>771711</t>
+          <t>840040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>741962</t>
+          <t>810329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>797447</t>
+          <t>867138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>787363</t>
+          <t>650120</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>736236</t>
+          <t>630353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>861801</t>
+          <t>668882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1559075</t>
+          <t>1490159</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1505517</t>
+          <t>1452853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1664756</t>
+          <t>1525474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>955295</t>
+          <t>1046031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>955295</t>
+          <t>1046031</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>955295</t>
+          <t>1046031</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>938622</t>
+          <t>818491</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>938622</t>
+          <t>818491</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>938622</t>
+          <t>818491</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1893917</t>
+          <t>1864522</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1893917</t>
+          <t>1864522</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1893917</t>
+          <t>1864522</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49680</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36661</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>70964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>158445</t>
+          <t>135089</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117826</t>
+          <t>119184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>250951</t>
+          <t>155876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>188920</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164042</t>
+          <t>165187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298051</t>
+          <t>211300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>388742</t>
+          <t>465808</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373606</t>
+          <t>448674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401761</t>
+          <t>479633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>636410</t>
+          <t>642501</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543904</t>
+          <t>621714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>677029</t>
+          <t>658406</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1025152</t>
+          <t>1108309</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935226</t>
+          <t>1085929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1069235</t>
+          <t>1132042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438422</t>
+          <t>519638</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438422</t>
+          <t>519638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438422</t>
+          <t>519638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>794855</t>
+          <t>777590</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>794855</t>
+          <t>777590</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>794855</t>
+          <t>777590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1233277</t>
+          <t>1297229</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1233277</t>
+          <t>1297229</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1233277</t>
+          <t>1297229</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>92775</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68945</t>
+          <t>77288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99722</t>
+          <t>108768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>99121</t>
+          <t>106903</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81956</t>
+          <t>89104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119289</t>
+          <t>128855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>183285</t>
+          <t>184258</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167432</t>
+          <t>168211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192198</t>
+          <t>191842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>610257</t>
+          <t>678091</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>594084</t>
+          <t>662098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>624861</t>
+          <t>693578</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>793542</t>
+          <t>862350</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>773374</t>
+          <t>840398</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>810707</t>
+          <t>880149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>198857</t>
+          <t>198386</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>198857</t>
+          <t>198386</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>198857</t>
+          <t>198386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>693806</t>
+          <t>770866</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>693806</t>
+          <t>770866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>693806</t>
+          <t>770866</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>892663</t>
+          <t>969253</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>892663</t>
+          <t>969253</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>892663</t>
+          <t>969253</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>502137</t>
+          <t>560553</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>383536</t>
+          <t>514101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>567668</t>
+          <t>605695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>612343</t>
+          <t>636651</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>495061</t>
+          <t>601094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>697540</t>
+          <t>678505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1114480</t>
+          <t>1197204</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>957674</t>
+          <t>1134735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1226099</t>
+          <t>1256075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2645464</t>
+          <t>2631913</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2579933</t>
+          <t>2586771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2764065</t>
+          <t>2678365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2776776</t>
+          <t>2789690</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2691579</t>
+          <t>2747836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2894058</t>
+          <t>2825247</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5422240</t>
+          <t>5421602</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5310621</t>
+          <t>5362731</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5579046</t>
+          <t>5484071</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3147601</t>
+          <t>3192466</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3147601</t>
+          <t>3192466</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3147601</t>
+          <t>3192466</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3389119</t>
+          <t>3426341</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3389119</t>
+          <t>3426341</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3389119</t>
+          <t>3426341</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6536720</t>
+          <t>6618806</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6536720</t>
+          <t>6618806</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6536720</t>
+          <t>6618806</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
